--- a/data/trans_orig/P3A_R1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112977</t>
+          <t>113729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152484</t>
+          <t>153706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71446</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103374</t>
+          <t>101894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193234</t>
+          <t>194923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246209</t>
+          <t>245663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320410</t>
+          <t>319188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359917</t>
+          <t>359165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203306</t>
+          <t>204786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235234</t>
+          <t>234983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533366</t>
+          <t>533912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586341</t>
+          <t>584652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84983</t>
+          <t>84110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121830</t>
+          <t>121253</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68655</t>
+          <t>70162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102622</t>
+          <t>104620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>165280</t>
+          <t>163384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210938</t>
+          <t>211953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>245104</t>
+          <t>245681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>281951</t>
+          <t>282824</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>269243</t>
+          <t>267245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>303210</t>
+          <t>301703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>527861</t>
+          <t>526846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>573519</t>
+          <t>575415</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,89%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114004</t>
+          <t>113105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154967</t>
+          <t>154249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29219</t>
+          <t>30595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135034</t>
+          <t>133902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177251</t>
+          <t>177679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387422</t>
+          <t>388140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>428385</t>
+          <t>429284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138563</t>
+          <t>137187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154630</t>
+          <t>154741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>532920</t>
+          <t>532492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>575137</t>
+          <t>576269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223955</t>
+          <t>223839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>284315</t>
+          <t>282922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76046</t>
+          <t>75728</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111487</t>
+          <t>114058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>311691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381898</t>
+          <t>381680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>954019</t>
+          <t>955412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1014379</t>
+          <t>1014495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601276</t>
+          <t>598705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>636717</t>
+          <t>637035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1569200</t>
+          <t>1569418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1638165</t>
+          <t>1639407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46357</t>
+          <t>46379</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75117</t>
+          <t>74514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33109</t>
+          <t>33363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58270</t>
+          <t>58556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84687</t>
+          <t>84584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124062</t>
+          <t>123863</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>275438</t>
+          <t>276041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304198</t>
+          <t>304176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>510482</t>
+          <t>510196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535643</t>
+          <t>535389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>795245</t>
+          <t>795444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>834620</t>
+          <t>834723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57101</t>
+          <t>58135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91797</t>
+          <t>91827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60316</t>
+          <t>60418</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>93464</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288973</t>
+          <t>289851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1153933</t>
+          <t>1153903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1188629</t>
+          <t>1187595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1447212</t>
+          <t>1450466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1483614</t>
+          <t>1483512</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>634433</t>
+          <t>631784</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>729533</t>
+          <t>726458</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368193</t>
+          <t>369403</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>441834</t>
+          <t>446942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1021891</t>
+          <t>1028237</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1150716</t>
+          <t>1156246</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2539775</t>
+          <t>2542850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2634875</t>
+          <t>2637524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2931738</t>
+          <t>2926630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3005379</t>
+          <t>3004169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5492164</t>
+          <t>5486634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5620989</t>
+          <t>5614643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136763</t>
+          <t>138077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177818</t>
+          <t>178243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78313</t>
+          <t>79909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112449</t>
+          <t>114776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>226810</t>
+          <t>225332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>282519</t>
+          <t>279371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259393</t>
+          <t>258968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300448</t>
+          <t>299134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202005</t>
+          <t>199678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>236141</t>
+          <t>234545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>469146</t>
+          <t>472294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>524855</t>
+          <t>526333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>133217</t>
+          <t>131773</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173185</t>
+          <t>174059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63782</t>
+          <t>64187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97189</t>
+          <t>97377</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>205632</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259467</t>
+          <t>259400</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>245612</t>
+          <t>244738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285580</t>
+          <t>287024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>240822</t>
+          <t>240634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>274229</t>
+          <t>273824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497341</t>
+          <t>497408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>551176</t>
+          <t>550070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175520</t>
+          <t>174528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>222286</t>
+          <t>223966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39256</t>
+          <t>39805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64828</t>
+          <t>66160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223976</t>
+          <t>224836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279174</t>
+          <t>278432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407129</t>
+          <t>405449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453895</t>
+          <t>454887</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195301</t>
+          <t>193969</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220873</t>
+          <t>220324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610370</t>
+          <t>611112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>665568</t>
+          <t>664708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279800</t>
+          <t>279972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>342223</t>
+          <t>340036</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123226</t>
+          <t>118779</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166291</t>
+          <t>166949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418108</t>
+          <t>414380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>496916</t>
+          <t>496753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>816786</t>
+          <t>818973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879209</t>
+          <t>879037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598365</t>
+          <t>597707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>641430</t>
+          <t>645877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1426750</t>
+          <t>1426913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1505558</t>
+          <t>1509286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101183</t>
+          <t>102576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141026</t>
+          <t>140559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66829</t>
+          <t>66434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102362</t>
+          <t>101819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178286</t>
+          <t>177698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228530</t>
+          <t>233141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368511</t>
+          <t>368978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408354</t>
+          <t>406961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659160</t>
+          <t>659703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694693</t>
+          <t>695088</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1042528</t>
+          <t>1037917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1092772</t>
+          <t>1093360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>59862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92639</t>
+          <t>96290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60576</t>
+          <t>60805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93203</t>
+          <t>96645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261669</t>
+          <t>262427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1016712</t>
+          <t>1013061</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1049661</t>
+          <t>1049489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1283030</t>
+          <t>1279588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1315657</t>
+          <t>1315428</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>887559</t>
+          <t>886801</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1002050</t>
+          <t>997382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>482615</t>
+          <t>483839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>568257</t>
+          <t>573396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1402730</t>
+          <t>1400115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1546430</t>
+          <t>1534715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2418800</t>
+          <t>2423468</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2533291</t>
+          <t>2534049</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2979867</t>
+          <t>2974728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3065509</t>
+          <t>3064285</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5422545</t>
+          <t>5434260</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5566245</t>
+          <t>5568860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149078</t>
+          <t>149817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190621</t>
+          <t>190496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96143</t>
+          <t>96705</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131315</t>
+          <t>130061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>254972</t>
+          <t>258530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312373</t>
+          <t>312566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>237623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279041</t>
+          <t>278302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215740</t>
+          <t>216994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250912</t>
+          <t>250350</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462801</t>
+          <t>462608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520202</t>
+          <t>516644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159622</t>
+          <t>160689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>200957</t>
+          <t>202727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>104199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142028</t>
+          <t>140649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>272311</t>
+          <t>271950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>328702</t>
+          <t>327396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176270</t>
+          <t>174500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217605</t>
+          <t>216538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230245</t>
+          <t>231624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268402</t>
+          <t>268074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>420798</t>
+          <t>422104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>477189</t>
+          <t>477550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174123</t>
+          <t>175739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218303</t>
+          <t>219788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>33497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58005</t>
+          <t>57264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217012</t>
+          <t>214707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268534</t>
+          <t>267125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301791</t>
+          <t>300306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>345971</t>
+          <t>344355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108118</t>
+          <t>108859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132741</t>
+          <t>132626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>417683</t>
+          <t>419092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>469205</t>
+          <t>471510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,71%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>370289</t>
+          <t>370910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>435993</t>
+          <t>439739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147199</t>
+          <t>146529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194268</t>
+          <t>191193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>531338</t>
+          <t>529496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>613221</t>
+          <t>611767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>709232</t>
+          <t>705486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>774936</t>
+          <t>774315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>627601</t>
+          <t>630676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674670</t>
+          <t>675340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1353872</t>
+          <t>1355326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1435755</t>
+          <t>1437597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123078</t>
+          <t>122312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165027</t>
+          <t>165362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81412</t>
+          <t>81786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118459</t>
+          <t>118861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215485</t>
+          <t>212960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271203</t>
+          <t>269670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455679</t>
+          <t>455344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>497628</t>
+          <t>498394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>618831</t>
+          <t>618429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>655878</t>
+          <t>655504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1086793</t>
+          <t>1088326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1142511</t>
+          <t>1145036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>87194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>127663</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89149</t>
+          <t>91184</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128700</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275530</t>
+          <t>275804</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284210</t>
+          <t>284203</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>955167</t>
+          <t>954362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>995568</t>
+          <t>994831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1238635</t>
+          <t>1235749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1278186</t>
+          <t>1276151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1044671</t>
+          <t>1039015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1158825</t>
+          <t>1155514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>609324</t>
+          <t>611359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>700156</t>
+          <t>698137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1684260</t>
+          <t>1683999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1828041</t>
+          <t>1823602</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2217856</t>
+          <t>2221167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2332010</t>
+          <t>2337666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2826478</t>
+          <t>2828497</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2917310</t>
+          <t>2915275</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5075274</t>
+          <t>5079713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5219055</t>
+          <t>5219316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174334</t>
+          <t>172272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>220434</t>
+          <t>218041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132950</t>
+          <t>132801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167999</t>
+          <t>165592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318283</t>
+          <t>320749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>372280</t>
+          <t>375796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284778</t>
+          <t>287171</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330878</t>
+          <t>332940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278774</t>
+          <t>281181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313823</t>
+          <t>313972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>579705</t>
+          <t>576189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>633702</t>
+          <t>631236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137232</t>
+          <t>137126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180030</t>
+          <t>179138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94527</t>
+          <t>94924</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123570</t>
+          <t>125275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>239604</t>
+          <t>239744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>291136</t>
+          <t>291112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271716</t>
+          <t>272608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314514</t>
+          <t>314620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>259010</t>
+          <t>257305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>288053</t>
+          <t>287656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>543190</t>
+          <t>543214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>594722</t>
+          <t>594582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46242</t>
+          <t>55474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221542</t>
+          <t>225243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32301</t>
+          <t>32145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>50461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71253</t>
+          <t>84552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256824</t>
+          <t>256419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446722</t>
+          <t>443021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622022</t>
+          <t>612790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116237</t>
+          <t>115884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134044</t>
+          <t>134200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>577785</t>
+          <t>578190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>763356</t>
+          <t>750057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276309</t>
+          <t>278314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>337506</t>
+          <t>343613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108485</t>
+          <t>113817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>272370</t>
+          <t>274025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>374711</t>
+          <t>360544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>592169</t>
+          <t>585085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>697313</t>
+          <t>691206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>758510</t>
+          <t>756505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705724</t>
+          <t>704069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>869609</t>
+          <t>864277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1420743</t>
+          <t>1427827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1638201</t>
+          <t>1652368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92768</t>
+          <t>91473</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132468</t>
+          <t>132151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107264</t>
+          <t>109932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171112</t>
+          <t>171361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209963</t>
+          <t>208287</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289295</t>
+          <t>290845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>342578</t>
+          <t>342895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>382278</t>
+          <t>383573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>670223</t>
+          <t>669974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734071</t>
+          <t>731403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1027086</t>
+          <t>1025536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1106418</t>
+          <t>1108094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16229</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54705</t>
+          <t>54763</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81901</t>
+          <t>81837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58072</t>
+          <t>58016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91116</t>
+          <t>89082</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224278</t>
+          <t>225652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238603</t>
+          <t>238739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679470</t>
+          <t>679534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>706666</t>
+          <t>706608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>910762</t>
+          <t>912796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>943806</t>
+          <t>943862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>727956</t>
+          <t>684551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1004966</t>
+          <t>1008261</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>580689</t>
+          <t>597762</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>784895</t>
+          <t>786080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1364778</t>
+          <t>1426381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1756426</t>
+          <t>1767307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2370628</t>
+          <t>2367333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2647638</t>
+          <t>2691043</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2791603</t>
+          <t>2790418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2995809</t>
+          <t>2978736</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5195666</t>
+          <t>5184785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5587314</t>
+          <t>5525711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113729</t>
+          <t>111442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153706</t>
+          <t>152331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71697</t>
+          <t>70596</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101894</t>
+          <t>102312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194923</t>
+          <t>192222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>245663</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>319188</t>
+          <t>320563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359165</t>
+          <t>361452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>204786</t>
+          <t>204368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234983</t>
+          <t>236084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>533912</t>
+          <t>533342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>584652</t>
+          <t>587353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84110</t>
+          <t>84491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121253</t>
+          <t>120305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70162</t>
+          <t>69390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104620</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163384</t>
+          <t>164522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211953</t>
+          <t>212499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>245681</t>
+          <t>246629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>282824</t>
+          <t>282443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267245</t>
+          <t>269427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>301703</t>
+          <t>302475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>526846</t>
+          <t>526300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>575415</t>
+          <t>574277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113105</t>
+          <t>115521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154249</t>
+          <t>155100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13041</t>
+          <t>13272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133902</t>
+          <t>133793</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177679</t>
+          <t>178584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>388140</t>
+          <t>387289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429284</t>
+          <t>426868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137187</t>
+          <t>137823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154741</t>
+          <t>154510</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>532492</t>
+          <t>531587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>576269</t>
+          <t>576378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223839</t>
+          <t>224205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282922</t>
+          <t>282613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75728</t>
+          <t>75365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114058</t>
+          <t>113783</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>311691</t>
+          <t>314933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381680</t>
+          <t>381115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>955412</t>
+          <t>955721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1014495</t>
+          <t>1014129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598705</t>
+          <t>598980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>637035</t>
+          <t>637398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1569418</t>
+          <t>1569983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1639407</t>
+          <t>1636165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46379</t>
+          <t>46577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74514</t>
+          <t>75131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>32437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58556</t>
+          <t>58127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84584</t>
+          <t>85979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123863</t>
+          <t>125115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276041</t>
+          <t>275424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304176</t>
+          <t>303978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>510196</t>
+          <t>510625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>535389</t>
+          <t>536315</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>795444</t>
+          <t>794192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>834723</t>
+          <t>833328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58135</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91827</t>
+          <t>90491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60418</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93464</t>
+          <t>92651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289851</t>
+          <t>288804</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1153903</t>
+          <t>1155239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1187595</t>
+          <t>1186637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1450466</t>
+          <t>1451279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1483512</t>
+          <t>1485287</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>631784</t>
+          <t>637233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>726458</t>
+          <t>733028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369403</t>
+          <t>367690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>446942</t>
+          <t>441936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1028237</t>
+          <t>1023573</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1156246</t>
+          <t>1147206</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2542850</t>
+          <t>2536280</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2637524</t>
+          <t>2632075</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2926630</t>
+          <t>2931636</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3004169</t>
+          <t>3005882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5486634</t>
+          <t>5495674</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5614643</t>
+          <t>5619307</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138077</t>
+          <t>135239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178243</t>
+          <t>178516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79909</t>
+          <t>79654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114776</t>
+          <t>111855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225332</t>
+          <t>229727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279371</t>
+          <t>279704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258968</t>
+          <t>258695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299134</t>
+          <t>301972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199678</t>
+          <t>202599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234545</t>
+          <t>234800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>472294</t>
+          <t>471961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>526333</t>
+          <t>521938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>131901</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174059</t>
+          <t>175060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64187</t>
+          <t>64285</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97377</t>
+          <t>97584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>206738</t>
+          <t>206860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259400</t>
+          <t>259442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244738</t>
+          <t>243737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287024</t>
+          <t>286896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>240634</t>
+          <t>240427</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>273824</t>
+          <t>273726</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497408</t>
+          <t>497366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>550070</t>
+          <t>549948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174528</t>
+          <t>173691</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>223966</t>
+          <t>222038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39805</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66160</t>
+          <t>66659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224836</t>
+          <t>223989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278432</t>
+          <t>277838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405449</t>
+          <t>407377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>454887</t>
+          <t>455724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>193969</t>
+          <t>193470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220324</t>
+          <t>219808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611112</t>
+          <t>611706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664708</t>
+          <t>665555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279972</t>
+          <t>278980</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>340036</t>
+          <t>342661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118779</t>
+          <t>119308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166949</t>
+          <t>164481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>414380</t>
+          <t>411526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>496753</t>
+          <t>492384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>818973</t>
+          <t>816348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879037</t>
+          <t>880029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597707</t>
+          <t>600175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645877</t>
+          <t>645348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1426913</t>
+          <t>1431282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1509286</t>
+          <t>1512140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,61%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102576</t>
+          <t>101250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140559</t>
+          <t>139555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66434</t>
+          <t>66118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>102637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177698</t>
+          <t>178821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>233141</t>
+          <t>231030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368978</t>
+          <t>369982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>406961</t>
+          <t>408287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659703</t>
+          <t>658885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>695088</t>
+          <t>695404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1037917</t>
+          <t>1040028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1093360</t>
+          <t>1092237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59862</t>
+          <t>59779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96290</t>
+          <t>93735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>59782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96645</t>
+          <t>94319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262427</t>
+          <t>261799</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1013061</t>
+          <t>1015616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1049489</t>
+          <t>1049572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1279588</t>
+          <t>1281914</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1315428</t>
+          <t>1316451</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>886801</t>
+          <t>890153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>997382</t>
+          <t>992195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>483839</t>
+          <t>484973</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>573396</t>
+          <t>575140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1400115</t>
+          <t>1394112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1534715</t>
+          <t>1541280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2423468</t>
+          <t>2428655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2534049</t>
+          <t>2530697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2974728</t>
+          <t>2972984</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3064285</t>
+          <t>3063151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5434260</t>
+          <t>5427695</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5568860</t>
+          <t>5574863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149817</t>
+          <t>151656</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190496</t>
+          <t>192547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96705</t>
+          <t>95742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130061</t>
+          <t>130390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>258530</t>
+          <t>257339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312566</t>
+          <t>309471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237623</t>
+          <t>235572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>278302</t>
+          <t>276463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216994</t>
+          <t>216665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250350</t>
+          <t>251313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462608</t>
+          <t>465703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516644</t>
+          <t>517835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,8%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160689</t>
+          <t>159354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202727</t>
+          <t>200292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104199</t>
+          <t>104051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140649</t>
+          <t>139833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>271950</t>
+          <t>274359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327396</t>
+          <t>330406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174500</t>
+          <t>176935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216538</t>
+          <t>217873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231624</t>
+          <t>232440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268074</t>
+          <t>268222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422104</t>
+          <t>419094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>477550</t>
+          <t>475141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175739</t>
+          <t>174416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>219788</t>
+          <t>218750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33497</t>
+          <t>34505</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>58157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214707</t>
+          <t>217699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267125</t>
+          <t>269271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300306</t>
+          <t>301344</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>344355</t>
+          <t>345678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108859</t>
+          <t>107966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132626</t>
+          <t>131618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>419092</t>
+          <t>416946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>471510</t>
+          <t>468518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>370910</t>
+          <t>366827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>439739</t>
+          <t>434282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146529</t>
+          <t>146487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191193</t>
+          <t>194609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>529496</t>
+          <t>528521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>611767</t>
+          <t>612025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>705486</t>
+          <t>710943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>774315</t>
+          <t>778398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630676</t>
+          <t>627260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>675340</t>
+          <t>675382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1355326</t>
+          <t>1355068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1437597</t>
+          <t>1438572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122312</t>
+          <t>122408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165362</t>
+          <t>165331</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81786</t>
+          <t>82430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118861</t>
+          <t>117367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212960</t>
+          <t>212206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269670</t>
+          <t>271618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455344</t>
+          <t>455375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498394</t>
+          <t>498298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>618429</t>
+          <t>619923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>655504</t>
+          <t>654860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1088326</t>
+          <t>1086378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1145036</t>
+          <t>1145790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87194</t>
+          <t>86079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127663</t>
+          <t>126247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91184</t>
+          <t>91103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>132039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>275804</t>
+          <t>275094</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284203</t>
+          <t>284189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>954362</t>
+          <t>955778</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>994831</t>
+          <t>995946</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1235749</t>
+          <t>1235296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1276151</t>
+          <t>1276232</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1039015</t>
+          <t>1043844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1155514</t>
+          <t>1153815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>611359</t>
+          <t>606821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>698137</t>
+          <t>702243</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1683999</t>
+          <t>1675571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1823602</t>
+          <t>1822906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2221167</t>
+          <t>2222866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2337666</t>
+          <t>2332837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2828497</t>
+          <t>2824391</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2915275</t>
+          <t>2919813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5079713</t>
+          <t>5080409</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5219316</t>
+          <t>5227744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>196011</t>
+          <t>214305</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172272</t>
+          <t>190510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218041</t>
+          <t>238809</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>149616</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132801</t>
+          <t>142899</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165592</t>
+          <t>177913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>345627</t>
+          <t>374085</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>320749</t>
+          <t>343735</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>375796</t>
+          <t>402135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>309201</t>
+          <t>336313</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287171</t>
+          <t>311809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332940</t>
+          <t>360108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>297157</t>
+          <t>327954</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281181</t>
+          <t>309821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313972</t>
+          <t>344835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>606358</t>
+          <t>664267</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>576189</t>
+          <t>636217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631236</t>
+          <t>694617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951985</t>
+          <t>1038352</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>156479</t>
+          <t>168753</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137126</t>
+          <t>147625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179138</t>
+          <t>192495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108996</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94924</t>
+          <t>100210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125275</t>
+          <t>133268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>265475</t>
+          <t>284957</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>239744</t>
+          <t>256747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>291112</t>
+          <t>310941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>295267</t>
+          <t>313976</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272608</t>
+          <t>290234</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314620</t>
+          <t>335104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>273584</t>
+          <t>306938</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257305</t>
+          <t>289875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>287656</t>
+          <t>322933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>568851</t>
+          <t>620914</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>543214</t>
+          <t>594930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>594582</t>
+          <t>649124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451746</t>
+          <t>482729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834326</t>
+          <t>905871</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>135209</t>
+          <t>149188</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55474</t>
+          <t>128935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>225243</t>
+          <t>170519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40361</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32145</t>
+          <t>36779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>56841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>175571</t>
+          <t>193953</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84552</t>
+          <t>171651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256419</t>
+          <t>219704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>533055</t>
+          <t>322424</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443021</t>
+          <t>301093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>612790</t>
+          <t>342677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>142163</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115884</t>
+          <t>130088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134200</t>
+          <t>150150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>659038</t>
+          <t>464587</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>578190</t>
+          <t>438836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>750057</t>
+          <t>486889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>307276</t>
+          <t>337824</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>278314</t>
+          <t>308800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>343613</t>
+          <t>371443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>208737</t>
+          <t>228518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113817</t>
+          <t>204804</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>274025</t>
+          <t>251093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>516013</t>
+          <t>566343</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360544</t>
+          <t>527828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>585085</t>
+          <t>607237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>727543</t>
+          <t>794019</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>691206</t>
+          <t>760400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>756505</t>
+          <t>823043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>769357</t>
+          <t>632693</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704069</t>
+          <t>610118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>864277</t>
+          <t>656407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1496899</t>
+          <t>1426711</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1427827</t>
+          <t>1385817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1652368</t>
+          <t>1465226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>111214</t>
+          <t>124221</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91473</t>
+          <t>103587</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132151</t>
+          <t>147607</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>145260</t>
+          <t>157351</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109932</t>
+          <t>140435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171361</t>
+          <t>179049</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>281572</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>208287</t>
+          <t>253318</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>290845</t>
+          <t>307772</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>363832</t>
+          <t>443743</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>342895</t>
+          <t>420357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383573</t>
+          <t>464377</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>696075</t>
+          <t>673499</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>669974</t>
+          <t>651801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731403</t>
+          <t>690415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1059908</t>
+          <t>1117242</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1025536</t>
+          <t>1091042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1108094</t>
+          <t>1145496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66363</t>
+          <t>71343</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54763</t>
+          <t>58353</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81837</t>
+          <t>86744</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,17 +10418,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>78256</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58016</t>
+          <t>64738</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89082</t>
+          <t>94579</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>234325</t>
+          <t>230316</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225652</t>
+          <t>220314</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238739</t>
+          <t>235254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>695008</t>
+          <t>772938</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679534</t>
+          <t>757537</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>706608</t>
+          <t>785928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,17 +10531,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>929333</t>
+          <t>1003253</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>912796</t>
+          <t>986930</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>943862</t>
+          <t>1016771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>912372</t>
+          <t>1001204</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>684551</t>
+          <t>944475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1008261</t>
+          <t>1058295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>719332</t>
+          <t>777963</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>597762</t>
+          <t>734299</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>786080</t>
+          <t>817691</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1631703</t>
+          <t>1779167</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1426381</t>
+          <t>1706869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1767307</t>
+          <t>1847004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2463222</t>
+          <t>2440789</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2367333</t>
+          <t>2383698</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2691043</t>
+          <t>2497518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2857166</t>
+          <t>2856185</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2790418</t>
+          <t>2816457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2978736</t>
+          <t>2899849</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5320389</t>
+          <t>5296973</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5184785</t>
+          <t>5229136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5525711</t>
+          <t>5369271</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375594</t>
+          <t>3441993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576498</t>
+          <t>3634148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952092</t>
+          <t>7076140</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
